--- a/questionnaire_templates/022_rejection_sensitivity_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/022_rejection_sensitivity_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro_page</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_1</t>
+          <t>rejection_sensitivity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,53 +554,53 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_2</t>
+          <t>emotional_reactions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How much do you experience rejection sensitivity?</t>
+          <t>When feeling rejected or disappointed, I often feel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_3</t>
+          <t>feelings_before_rejection</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How much do you experience rejection sensitivity?</t>
+          <t>Before feeling rejected or disappointed, I often feel</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>emotional_reactions_1_1</t>
+          <t>reactions_to_rejection</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>When feeling rejected or disappointed, I often feel</t>
+          <t>Reactions to feeling rejected or disappointed</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>emotional_reactions_2_2</t>
+          <t>feelings_after_rejection</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>When feeling rejected or disappointed, I often feel</t>
+          <t>After feeling rejected or disappointed, I often feel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,64 +658,64 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emotional_reactions_3_3</t>
+          <t>typical_reaction</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>When feeling rejected or disappointed, I often feel</t>
+          <t>What is your typical reaction when faced with rejection or disappointment?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_1_4</t>
+          <t>take_ownership</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>After feeling rejected or disappointed, I often feel</t>
+          <t>Do you often take responsibility for the rejection or disappointment?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_2_5</t>
+          <t>rationalize</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>After feeling rejected or disappointed, I often feel</t>
+          <t>Do you often rationalize or intellectualize the rejection or disappointment?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_3_6</t>
+          <t>typical_emotional_state</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>After feeling rejected or disappointed, I often feel</t>
+          <t>What is your typical emotional state when you feel rejected or disappointed?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,202 +750,202 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>feelings_before_rejection_1_7</t>
+          <t>behavioral_response</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Before feeling rejected or disappointed, I often feel</t>
+          <t>What is your typical behavioral response when faced with rejection or disappointment?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>feelings_before_rejection_2_8</t>
+          <t>take_action</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Before feeling rejected or disappointed, I often feel</t>
+          <t>Do you often try to take action or do something to counter the rejection or disappointment?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>feelings_before_rejection_3_9</t>
+          <t>feel_stuck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Before feeling rejected or disappointed, I often feel</t>
+          <t>Do you often feel like you're stuck or frozen in place when feeling rejected or disappointed?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_1_10</t>
+          <t>feel_overwhelmed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>After feeling rejected or disappointed, I often feel</t>
+          <t>Do you often feel like you're losing control or are overwhelmed when feeling rejected or disappointed?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_2_11</t>
+          <t>emotional_shutdown</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>After feeling rejected or disappointed, I often feel</t>
+          <t>Do you often react with a sense of numbness or emotional shutdown?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_3_12</t>
+          <t>denial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>After feeling rejected or disappointed, I often feel</t>
+          <t>Do you often feel like you're stuck in a state of denial when feeling rejected or disappointed?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>reactions_to_rejection_1_13</t>
+          <t>fear_anxiety</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Reactions to feeling rejected or disappointed</t>
+          <t>Do you often react with fear or anxiety when faced with rejection or disappointment?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>reactions_to_rejection_2_14</t>
+          <t>run_away</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Reactions to feeling rejected or disappointed</t>
+          <t>Do you often feel like you're running away or escaping when feeling rejected or disappointed?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>reactions_to_rejection_3_15</t>
+          <t>hide_avoid</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Reactions to feeling rejected or disappointed</t>
+          <t>Do you often feel like you're hiding or avoiding when feeling rejected or disappointed?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -957,18 +957,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>reactions_to_rejection_1_16</t>
+          <t>emotional_state</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Reactions to feeling rejected or disappointed</t>
+          <t>Emotional State</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -980,110 +980,110 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>reactions_to_rejection_2_17</t>
+          <t>behavioral_response_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Reactions to feeling rejected or disappointed</t>
+          <t>Behavioral Response 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>reactions_to_rejection_3_18</t>
+          <t>take_action_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Reactions to feeling rejected or disappointed</t>
+          <t>Take Action 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>reactions_to_rejection_1_19</t>
+          <t>emotional_shutdown_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Reactions to feeling rejected or disappointed</t>
+          <t>Emotional Shutdown 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>reactions_to_rejection_2_20</t>
+          <t>denial_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reactions to feeling rejected or disappointed</t>
+          <t>Denial 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>reactions_to_rejection_3_21</t>
+          <t>fear_anxiety_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reactions to feeling rejected or disappointed</t>
+          <t>Fear Anxiety 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,2446 +1126,984 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_1_choices</t>
+          <t>rejection_sensitivity_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_1_choices</t>
+          <t>rejection_sensitivity_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_1_choices</t>
+          <t>rejection_sensitivity_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>moderately</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Moderately</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_1_choices</t>
+          <t>rejection_sensitivity_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>strongly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Strongly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_1_choices</t>
+          <t>emotional_reactions_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Sad</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_1_choices</t>
+          <t>emotional_reactions_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Angry</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_2_choices</t>
+          <t>emotional_reactions_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>bored</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Bored</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_2_choices</t>
+          <t>emotional_reactions_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>anxious</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Anxious</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_2_choices</t>
+          <t>emotional_reactions_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>hopeless</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Hopeless</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_2_choices</t>
+          <t>emotional_reactions_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>confused</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Confused</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_2_choices</t>
+          <t>feelings_before_rejection_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Sad</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_2_choices</t>
+          <t>feelings_before_rejection_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Angry</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_3_choices</t>
+          <t>feelings_before_rejection_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>bored</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Bored</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_3_choices</t>
+          <t>feelings_before_rejection_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>anxious</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Anxious</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_3_choices</t>
+          <t>feelings_before_rejection_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>hopeless</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Hopeless</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_3_choices</t>
+          <t>feelings_before_rejection_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>confused</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Confused</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_3_choices</t>
+          <t>reactions_to_rejection_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Run</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>rejection_sensitivity_scale_3_choices</t>
+          <t>reactions_to_rejection_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>hide</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Hide</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>emotional_reactions_1_1_choices</t>
+          <t>reactions_to_rejection_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>avoid</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Avoid</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>emotional_reactions_1_1_choices</t>
+          <t>reactions_to_rejection_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Attack</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>emotional_reactions_1_1_choices</t>
+          <t>reactions_to_rejection_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bored</t>
+          <t>freeze</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bored</t>
+          <t>Freeze</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>emotional_reactions_1_1_choices</t>
+          <t>reactions_to_rejection_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>anxious</t>
+          <t>stay_calm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Anxious</t>
+          <t>Stay Calm</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>emotional_reactions_1_1_choices</t>
+          <t>feelings_after_rejection_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>hopeless</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hopeless</t>
+          <t>Sad</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>emotional_reactions_1_1_choices</t>
+          <t>feelings_after_rejection_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>confused</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Confused</t>
+          <t>Angry</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>emotional_reactions_2_2_choices</t>
+          <t>feelings_after_rejection_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>bored</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Bored</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>emotional_reactions_2_2_choices</t>
+          <t>feelings_after_rejection_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>anxious</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Anxious</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>emotional_reactions_2_2_choices</t>
+          <t>feelings_after_rejection_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>bored</t>
+          <t>hopeless</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bored</t>
+          <t>Hopeless</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>emotional_reactions_2_2_choices</t>
+          <t>feelings_after_rejection_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>anxious</t>
+          <t>confused</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Anxious</t>
+          <t>Confused</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>emotional_reactions_2_2_choices</t>
+          <t>typical_reaction_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hopeless</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hopeless</t>
+          <t>Run</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>emotional_reactions_2_2_choices</t>
+          <t>typical_reaction_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>confused</t>
+          <t>hide</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Confused</t>
+          <t>Hide</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>emotional_reactions_3_3_choices</t>
+          <t>typical_reaction_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>avoid</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Avoid</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>emotional_reactions_3_3_choices</t>
+          <t>typical_reaction_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Attack</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>emotional_reactions_3_3_choices</t>
+          <t>typical_reaction_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bored</t>
+          <t>freeze</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bored</t>
+          <t>Freeze</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>emotional_reactions_3_3_choices</t>
+          <t>typical_reaction_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>anxious</t>
+          <t>stay_calm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Anxious</t>
+          <t>Stay Calm</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>emotional_reactions_3_3_choices</t>
+          <t>typical_emotional_state_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>hopeless</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hopeless</t>
+          <t>Sad</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>emotional_reactions_3_3_choices</t>
+          <t>typical_emotional_state_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>confused</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Confused</t>
+          <t>Angry</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_1_4_choices</t>
+          <t>typical_emotional_state_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>bored</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Bored</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_1_4_choices</t>
+          <t>typical_emotional_state_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>anxious</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Anxious</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_1_4_choices</t>
+          <t>typical_emotional_state_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bored</t>
+          <t>hopeless</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bored</t>
+          <t>Hopeless</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_1_4_choices</t>
+          <t>typical_emotional_state_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>anxious</t>
+          <t>confused</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Anxious</t>
+          <t>Confused</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_1_4_choices</t>
+          <t>behavioral_response_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>hopeless</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hopeless</t>
+          <t>Run</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_1_4_choices</t>
+          <t>behavioral_response_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>confused</t>
+          <t>hide</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Confused</t>
+          <t>Hide</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_2_5_choices</t>
+          <t>behavioral_response_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>avoid</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Avoid</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_2_5_choices</t>
+          <t>behavioral_response_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Attack</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_2_5_choices</t>
+          <t>behavioral_response_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>bored</t>
+          <t>freeze</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bored</t>
+          <t>Freeze</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_2_5_choices</t>
+          <t>behavioral_response_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>anxious</t>
+          <t>stay_calm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Anxious</t>
+          <t>Stay Calm</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_2_5_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>hopeless</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hopeless</t>
+          <t>Sad</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_2_5_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>confused</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Confused</t>
+          <t>Angry</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_3_6_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>bored</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Bored</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_3_6_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>anxious</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Anxious</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_3_6_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bored</t>
+          <t>hopeless</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bored</t>
+          <t>Hopeless</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_3_6_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>anxious</t>
+          <t>confused</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Anxious</t>
+          <t>Confused</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_3_6_choices</t>
+          <t>behavioral_response_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>hopeless</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hopeless</t>
+          <t>Run</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>feelings_after_rejection_3_6_choices</t>
+          <t>behavioral_response_2_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>confused</t>
+          <t>hide</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Confused</t>
+          <t>Hide</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>feelings_before_rejection_1_7_choices</t>
+          <t>behavioral_response_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>avoid</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Avoid</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>feelings_before_rejection_1_7_choices</t>
+          <t>behavioral_response_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Attack</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>feelings_before_rejection_1_7_choices</t>
+          <t>behavioral_response_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>bored</t>
+          <t>freeze</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bored</t>
+          <t>Freeze</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>feelings_before_rejection_1_7_choices</t>
+          <t>behavioral_response_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>anxious</t>
+          <t>stay_calm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
-        <is>
-          <t>Anxious</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_1_7_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>hopeless</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Hopeless</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_1_7_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>confused</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Confused</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_2_8_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>sad</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Sad</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_2_8_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>angry</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_2_8_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>bored</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Bored</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_2_8_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>anxious</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Anxious</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_2_8_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>hopeless</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Hopeless</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_2_8_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>confused</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Confused</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_3_9_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>sad</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Sad</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_3_9_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>angry</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_3_9_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>bored</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Bored</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_3_9_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>anxious</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Anxious</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_3_9_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>hopeless</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Hopeless</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>feelings_before_rejection_3_9_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>confused</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Confused</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_1_10_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>sad</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Sad</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_1_10_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>angry</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_1_10_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>bored</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Bored</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_1_10_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>anxious</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Anxious</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_1_10_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>hopeless</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Hopeless</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_1_10_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>confused</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Confused</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_2_11_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>sad</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Sad</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_2_11_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>angry</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_2_11_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>bored</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Bored</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_2_11_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>anxious</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Anxious</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_2_11_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>hopeless</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Hopeless</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_2_11_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>confused</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Confused</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_3_12_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>sad</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Sad</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_3_12_choices</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>angry</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_3_12_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>bored</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Bored</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_3_12_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>anxious</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Anxious</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_3_12_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>hopeless</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Hopeless</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>feelings_after_rejection_3_12_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>confused</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Confused</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_13_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_13_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Hide</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_13_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>avoid</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_13_choices</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_13_choices</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>freeze</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_13_choices</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>stay_calm</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Stay Calm</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_14_choices</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_14_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Hide</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_14_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>avoid</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_14_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_14_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>freeze</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_14_choices</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>stay_calm</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Stay Calm</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_15_choices</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_15_choices</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Hide</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_15_choices</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>avoid</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_15_choices</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_15_choices</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>freeze</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_15_choices</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>stay_calm</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Stay Calm</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_16_choices</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_16_choices</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Hide</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_16_choices</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>avoid</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_16_choices</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_16_choices</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>freeze</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_16_choices</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>stay_calm</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Stay Calm</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_17_choices</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_17_choices</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Hide</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_17_choices</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>avoid</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_17_choices</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_17_choices</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>freeze</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_17_choices</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>stay_calm</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Stay Calm</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_18_choices</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_18_choices</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Hide</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_18_choices</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>avoid</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_18_choices</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_18_choices</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>freeze</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_18_choices</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>stay_calm</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Stay Calm</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_19_choices</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_19_choices</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Hide</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_19_choices</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>avoid</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_19_choices</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_19_choices</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>freeze</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_1_19_choices</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>stay_calm</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Stay Calm</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_20_choices</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_20_choices</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Hide</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_20_choices</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>avoid</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_20_choices</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_20_choices</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>freeze</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_2_20_choices</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>stay_calm</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Stay Calm</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_21_choices</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_21_choices</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>hide</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Hide</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_21_choices</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>avoid</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_21_choices</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_21_choices</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>freeze</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>reactions_to_rejection_3_21_choices</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>stay_calm</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
         <is>
           <t>Stay Calm</t>
         </is>
